--- a/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0002T0006Z000C1N65_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0002T0006Z000C1N65_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,10 +486,10 @@
         <v>15.56031588404874</v>
       </c>
       <c r="E2" t="n">
-        <v>5.477987343803977</v>
+        <v>5.336056253200616</v>
       </c>
       <c r="F2" t="n">
-        <v>4.511420271442091</v>
+        <v>3.972867904467833</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -518,10 +518,10 @@
         <v>19.82467498005006</v>
       </c>
       <c r="E3" t="n">
-        <v>5.477987343803977</v>
+        <v>5.336056253200616</v>
       </c>
       <c r="F3" t="n">
-        <v>4.511420271442091</v>
+        <v>3.972867904467833</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
         <v>8.863591818328896</v>
       </c>
       <c r="E4" t="n">
-        <v>5.477987343803977</v>
+        <v>5.336056253200616</v>
       </c>
       <c r="F4" t="n">
-        <v>4.511420271442091</v>
+        <v>3.972867904467833</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -561,6 +561,38 @@
         </is>
       </c>
       <c r="H4" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>W0035F0002T0006Z000C1N65.png</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>23.47796595691757</v>
+      </c>
+      <c r="D5" t="n">
+        <v>13.08580524877651</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5.336056253200616</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3.972867904467833</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>T1791L</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>G5</t>
         </is>

--- a/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0002T0006Z000C1N65_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0002T0006Z000C1N65_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>23.04481357618311</v>
+        <v>3.744782206129755</v>
       </c>
       <c r="D2" t="n">
-        <v>15.56031588404874</v>
+        <v>2.52855133115792</v>
       </c>
       <c r="E2" t="n">
-        <v>5.336056253200616</v>
+        <v>0.8671091411451002</v>
       </c>
       <c r="F2" t="n">
-        <v>3.972867904467833</v>
+        <v>0.6455910344760228</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>20.19917080872008</v>
+        <v>3.282365256417012</v>
       </c>
       <c r="D3" t="n">
-        <v>19.82467498005006</v>
+        <v>3.221509684258135</v>
       </c>
       <c r="E3" t="n">
-        <v>5.336056253200616</v>
+        <v>0.8671091411451002</v>
       </c>
       <c r="F3" t="n">
-        <v>3.972867904467833</v>
+        <v>0.6455910344760228</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>10.26574756868034</v>
+        <v>1.668183979910555</v>
       </c>
       <c r="D4" t="n">
-        <v>8.863591818328896</v>
+        <v>1.440333670478446</v>
       </c>
       <c r="E4" t="n">
-        <v>5.336056253200616</v>
+        <v>0.8671091411451002</v>
       </c>
       <c r="F4" t="n">
-        <v>3.972867904467833</v>
+        <v>0.6455910344760228</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>23.47796595691757</v>
+        <v>3.815169467999106</v>
       </c>
       <c r="D5" t="n">
-        <v>13.08580524877651</v>
+        <v>2.126443352926183</v>
       </c>
       <c r="E5" t="n">
-        <v>5.336056253200616</v>
+        <v>0.8671091411451002</v>
       </c>
       <c r="F5" t="n">
-        <v>3.972867904467833</v>
+        <v>0.6455910344760228</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
